--- a/Блокноты/Банеры/2026/05.03.26/Ключи Блокноты .xlsx
+++ b/Блокноты/Банеры/2026/05.03.26/Ключи Блокноты .xlsx
@@ -29,61 +29,61 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
-    <t>82 NtrRiodeJ82.PQTC.04.03.26 Рио-де-Жанейро собор Святого Себастьяна</t>
+    <t>82 NtrRiodeJ82.PQTC.05.03.26 Рио-де-Жанейро собор Святого Себастьяна</t>
   </si>
   <si>
     <t>Рио-де-Жанейро, Рио де Жанейро, Rio de Janeiro, город, citi, Бразилия, Brazil, достопримечательности, красивые места, красивый вид, собор, собор Святого Себастьяна, кафедральный собор, собор св себастьяна, cathedral of rio de janeiro</t>
   </si>
   <si>
-    <t>83 NtrRiodeJ83.PQTC.04.03.26 Рио-де-Жанейро Церковь Канделария</t>
+    <t>83 NtrRiodeJ83.PQTC.05.03.26 Рио-де-Жанейро Церковь Канделария</t>
   </si>
   <si>
     <t>Рио-де-Жанейро, Рио де Жанейро, Rio de Janeiro, город, citi, Бразилия, Brazil, достопримечательности, красивые места, красивый вид, церковь Канделирия, церковь, igreja de nossa senhora da candelária, igreja da candelaria, roman catholic church in brazil</t>
   </si>
   <si>
-    <t>84 NtrRiodeJ84.PQTC.04.03.26 Рио-де-Жанейро Церковь Канделария</t>
-  </si>
-  <si>
-    <t>85 NtrRiodeJ85.PQTC.04.03.26 Рио-де-Жанейро Муниципальный театр</t>
+    <t>84 NtrRiodeJ84.PQTC.05.03.26 Рио-де-Жанейро Церковь Канделария</t>
+  </si>
+  <si>
+    <t>85 NtrRiodeJ85.PQTC.05.03.26 Рио-де-Жанейро Муниципальный театр</t>
   </si>
   <si>
     <t>Рио-де-Жанейро, Рио де Жанейро, Rio de Janeiro, город, citi, Бразилия, Brazil, достопримечательности, красивые места, красивый вид, Муниципальный театр, театр, municipal theatre of rio de janeiro, municipal theater of sao paulo, teatro municipal do rio de janeiro</t>
   </si>
   <si>
-    <t>86 NtrRiodeJ86.PQTC.04.03.26 Рио-де-Жанейро Музей современного искусства</t>
+    <t>86 NtrRiodeJ86.PQTC.05.03.26 Рио-де-Жанейро Музей современного искусства</t>
   </si>
   <si>
     <t>Рио-де-Жанейро, Рио де Жанейро, Rio de Janeiro, город, citi, Бразилия, Brazil, достопримечательности, красивые места, красивый вид, музей, музей современного искусства, нитерой рио де жанейро, niteroi contemporary art museum</t>
   </si>
   <si>
-    <t>87 NtrRiodeJ87.PQTC.04.03.26 Рио-де-Жанейро монумент</t>
+    <t>87 NtrRiodeJ87.PQTC.05.03.26 Рио-де-Жанейро монумент</t>
   </si>
   <si>
     <t>Рио-де-Жанейро, Рио де Жанейро, Rio de Janeiro, город, citi, Бразилия, Brazil, достопримечательности, красивые места, красивый вид, монумент, горы, океан, атлантический океан, побережье, берег, гора Пан-ди-Асукар, гора, Pan-di-Asukar, гора сахарная голова</t>
   </si>
   <si>
-    <t>88 NtrRiodeJ88.PQTC.04.03.26 Рио-де-Жанейро Парк Лаге</t>
+    <t>88 NtrRiodeJ88.PQTC.05.03.26 Рио-де-Жанейро Парк Лаге</t>
   </si>
   <si>
     <t>Рио-де-Жанейро, Рио де Жанейро, Rio de Janeiro, город, citi, Бразилия, Brazil, достопримечательности, красивые места, красивый вид, горы, парк, парк Лаже, ботанический сад, сад, парк лаге рио де жанейро, jardim botanico do rio de janeiro</t>
   </si>
   <si>
-    <t>89 NtrRiodeJ89.PQTC.04.03.26 Рио-де-Жанейро Парк Лаге</t>
-  </si>
-  <si>
-    <t>90 NtrAlmaty90.PQTC.04.03.26 Алматы</t>
+    <t>89 NtrRiodeJ89.PQTC.05.03.26 Рио-де-Жанейро Парк Лаге</t>
+  </si>
+  <si>
+    <t>90 NtrAlmaty90.PQTC.05.03.26 Алматы</t>
   </si>
   <si>
     <t>Алматы, Алма-Ата, Казахстан, город, Красивый вид, красивые места, citi, Almaty, Alma Ata, Kazakhstan, холмы, горы</t>
   </si>
   <si>
-    <t>91 NtrAlmaty91.PQTC.04.03.26 Ночные Алматы</t>
+    <t>91 NtrAlmaty91.PQTC.05.03.26 Ночные Алматы</t>
   </si>
   <si>
     <t>Алматы, Алма-Ата, Казахстан, город, Красивый вид, красивые места, citi, Almaty, Alma Ata, Kazakhstan, холмы, горы, ночной вид, ночной город, ночной Алматы</t>
   </si>
   <si>
-    <t>92 NtrAlmaty92.PQTC.04.03.26 Ночные Алматы</t>
+    <t>92 NtrAlmaty92.PQTC.05.03.26 Ночные Алматы</t>
   </si>
 </sst>
 </file>
